--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EternalSH\GitHub\leetcode\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6DE5D5-B879-4DCF-BE9A-AA5643E95F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7722FD18-64CD-491D-B66A-B48EFC5D0449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="2480" windowWidth="38400" windowHeight="15410" activeTab="3" xr2:uid="{4A84287D-0BEF-40C6-AE57-6915C5D67076}"/>
+    <workbookView xWindow="19580" yWindow="1560" windowWidth="38400" windowHeight="15410" xr2:uid="{4A84287D-0BEF-40C6-AE57-6915C5D67076}"/>
   </bookViews>
   <sheets>
     <sheet name="C - C++ - Rust" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="10">
   <si>
     <t>Problem</t>
   </si>
@@ -108,8 +108,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -128,8 +129,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{454290D0-B282-4A62-85ED-B8792DDB0645}" name="Table1" displayName="Table1" ref="A1:D2" totalsRowShown="0">
-  <autoFilter ref="A1:D2" xr:uid="{454290D0-B282-4A62-85ED-B8792DDB0645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{454290D0-B282-4A62-85ED-B8792DDB0645}" name="Table1" displayName="Table1" ref="A1:D12" totalsRowShown="0">
+  <autoFilter ref="A1:D12" xr:uid="{454290D0-B282-4A62-85ED-B8792DDB0645}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D12">
+    <sortCondition ref="A1:A12"/>
+  </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3EEB4ACA-598F-4439-BD5E-33AC68A5D54B}" name="Problem"/>
     <tableColumn id="2" xr3:uid="{4F1EF198-1466-4B23-91D2-F6BCAEE62A28}" name="C"/>
@@ -457,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5775C85E-31DE-45E4-B410-9B035ABCC6F2}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
@@ -479,15 +483,107 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
         <v>470</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
         <v>4</v>
       </c>
     </row>

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EternalSH\GitHub\leetcode\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7722FD18-64CD-491D-B66A-B48EFC5D0449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E3A196-8B9D-4314-BFEA-2603FCB2EC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19580" yWindow="1560" windowWidth="38400" windowHeight="15410" xr2:uid="{4A84287D-0BEF-40C6-AE57-6915C5D67076}"/>
+    <workbookView xWindow="2480" yWindow="2480" windowWidth="38400" windowHeight="15410" xr2:uid="{4A84287D-0BEF-40C6-AE57-6915C5D67076}"/>
   </bookViews>
   <sheets>
     <sheet name="C - C++ - Rust" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t>Problem</t>
   </si>
@@ -108,9 +108,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,6 +484,9 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
@@ -496,7 +498,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">

--- a/summary.xlsx
+++ b/summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EternalSH\GitHub\leetcode\leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E3A196-8B9D-4314-BFEA-2603FCB2EC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE4C747-70DC-4A11-A033-60679DA0622D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="2480" windowWidth="38400" windowHeight="15410" xr2:uid="{4A84287D-0BEF-40C6-AE57-6915C5D67076}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="10">
   <si>
     <t>Problem</t>
   </si>
@@ -544,6 +544,9 @@
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
